--- a/output/quality_compounder.xlsx
+++ b/output/quality_compounder.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,100 +429,115 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>cash_from_operations_cr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>net_profit_margin_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>roce_percentage</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>market_cap_crore</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>pe_ratio</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>pb_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>dividend_yield_pct</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>net_profit</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>opm_percentage</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>broad_sector</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>dividend_payout_ratio_pct</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>roce_percentage</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>market_cap_crore</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>pe_ratio</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>pb_ratio</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>dividend_yield_pct</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>net_profit</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>opm_percentage</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>broad_sector</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>dividend_payout_ratio_pct</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>sector_relative_score</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>revenue_cagr_3yr</t>
         </is>
@@ -531,7 +546,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -540,68 +555,81 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>48.28</v>
+        <v>882</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>26.02</v>
       </c>
       <c r="E2" t="n">
-        <v>8.300000000000001</v>
+        <v>34.4</v>
       </c>
       <c r="F2" t="n">
-        <v>0.55</v>
+        <v>0.02</v>
       </c>
       <c r="G2" t="n">
-        <v>17651</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>667</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17.96</v>
+      </c>
       <c r="K2" t="n">
-        <v>88.79000000000001</v>
+        <v>29.17</v>
       </c>
       <c r="L2" t="n">
-        <v>32.2</v>
+        <v>28.47</v>
       </c>
       <c r="M2" t="n">
-        <v>1372183.55</v>
+        <v>53.8</v>
       </c>
       <c r="N2" t="n">
-        <v>44.57</v>
+        <v>1258520.29</v>
       </c>
       <c r="O2" t="n">
-        <v>9.91</v>
+        <v>60.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.65</v>
+        <v>5.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>50351</v>
+        <v>1.08</v>
       </c>
       <c r="R2" t="n">
-        <v>20829</v>
+        <v>4270</v>
       </c>
       <c r="S2" t="n">
-        <v>36</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
+        <v>1111</v>
+      </c>
+      <c r="T2" t="n">
+        <v>34</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="V2" t="n">
-        <v>24.29479715622616</v>
+        <v>47</v>
+      </c>
+      <c r="W2" t="n">
+        <v>74.0978734217103</v>
+      </c>
+      <c r="X2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>76.46921430165466</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -610,72 +638,81 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50.94</v>
+        <v>21183</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09</v>
+        <v>11.85</v>
       </c>
       <c r="E3" t="n">
-        <v>87.09999999999999</v>
+        <v>892.5700000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>1.66</v>
+        <v>0.02</v>
       </c>
       <c r="G3" t="n">
-        <v>50429</v>
+        <v>22.61</v>
       </c>
       <c r="H3" t="n">
-        <v>10.46</v>
+        <v>56.39</v>
       </c>
       <c r="I3" t="n">
+        <v>9424</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="K3" t="n">
+        <v>120.69</v>
+      </c>
+      <c r="L3" t="n">
+        <v>121.24</v>
+      </c>
+      <c r="M3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1040632.92</v>
+      </c>
+      <c r="O3" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="P3" t="n">
         <v>7.87</v>
       </c>
-      <c r="J3" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="K3" t="n">
-        <v>85.89</v>
-      </c>
-      <c r="L3" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>461188.15</v>
-      </c>
-      <c r="N3" t="n">
-        <v>78.69</v>
-      </c>
-      <c r="O3" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.62</v>
-      </c>
       <c r="Q3" t="n">
-        <v>240893</v>
+        <v>4.27</v>
       </c>
       <c r="R3" t="n">
-        <v>46099</v>
+        <v>68904</v>
       </c>
       <c r="S3" t="n">
-        <v>27</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>58</v>
+        <v>8167</v>
+      </c>
+      <c r="T3" t="n">
+        <v>16331</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="V3" t="n">
-        <v>13.63286455550641</v>
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>70.21066259469271</v>
+      </c>
+      <c r="X3" t="n">
+        <v>90.24625159260717</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>67.58091776468258</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -684,72 +721,81 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15.09</v>
+        <v>4175</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>16.12</v>
       </c>
       <c r="E4" t="n">
-        <v>58.33</v>
+        <v>117.75</v>
       </c>
       <c r="F4" t="n">
-        <v>0.57</v>
+        <v>0.1</v>
       </c>
       <c r="G4" t="n">
-        <v>11372</v>
+        <v>41.19</v>
       </c>
       <c r="H4" t="n">
-        <v>10.78</v>
+        <v>2.32</v>
       </c>
       <c r="I4" t="n">
-        <v>24.54</v>
+        <v>2938</v>
       </c>
       <c r="J4" t="n">
-        <v>29.46</v>
+        <v>14.55</v>
       </c>
       <c r="K4" t="n">
-        <v>85.44</v>
+        <v>14.85</v>
       </c>
       <c r="L4" t="n">
-        <v>17.3</v>
+        <v>15.44</v>
       </c>
       <c r="M4" t="n">
-        <v>1339586.09</v>
+        <v>185.43</v>
       </c>
       <c r="N4" t="n">
-        <v>37.9</v>
+        <v>1677775.19</v>
       </c>
       <c r="O4" t="n">
-        <v>6.71</v>
+        <v>54.96</v>
       </c>
       <c r="P4" t="n">
-        <v>3.88</v>
+        <v>14.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>48497</v>
+        <v>3.85</v>
       </c>
       <c r="R4" t="n">
-        <v>9610</v>
+        <v>24394</v>
       </c>
       <c r="S4" t="n">
-        <v>28</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>34</v>
+        <v>3933</v>
+      </c>
+      <c r="T4" t="n">
+        <v>24</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
       </c>
       <c r="V4" t="n">
-        <v>13.12675558948349</v>
+        <v>79</v>
+      </c>
+      <c r="W4" t="n">
+        <v>67.99817496750697</v>
+      </c>
+      <c r="X4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>18.28200866249903</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -758,72 +804,81 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>892.5700000000001</v>
+        <v>44338</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02</v>
+        <v>19.14</v>
       </c>
       <c r="E5" t="n">
-        <v>22.61</v>
+        <v>50.94</v>
       </c>
       <c r="F5" t="n">
-        <v>56.39</v>
+        <v>0.09</v>
       </c>
       <c r="G5" t="n">
-        <v>9424</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>19.31</v>
+        <v>1.66</v>
       </c>
       <c r="I5" t="n">
-        <v>120.69</v>
+        <v>50429</v>
       </c>
       <c r="J5" t="n">
-        <v>121.24</v>
+        <v>10.46</v>
       </c>
       <c r="K5" t="n">
-        <v>85.27</v>
+        <v>7.87</v>
       </c>
       <c r="L5" t="n">
-        <v>24.5</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>1040632.92</v>
+        <v>64.3</v>
       </c>
       <c r="N5" t="n">
-        <v>76.23</v>
+        <v>461188.15</v>
       </c>
       <c r="O5" t="n">
-        <v>7.87</v>
+        <v>78.69</v>
       </c>
       <c r="P5" t="n">
-        <v>4.27</v>
+        <v>6.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>68904</v>
+        <v>1.62</v>
       </c>
       <c r="R5" t="n">
-        <v>8167</v>
+        <v>240893</v>
       </c>
       <c r="S5" t="n">
-        <v>16331</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
+        <v>46099</v>
+      </c>
+      <c r="T5" t="n">
+        <v>27</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
       </c>
       <c r="V5" t="n">
-        <v>67.58091776468258</v>
+        <v>58</v>
+      </c>
+      <c r="W5" t="n">
+        <v>65.88670823293455</v>
+      </c>
+      <c r="X5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>13.63286455550641</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -832,72 +887,77 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>117.75</v>
+        <v>14170</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>41.37</v>
       </c>
       <c r="E6" t="n">
-        <v>41.19</v>
+        <v>48.28</v>
       </c>
       <c r="F6" t="n">
-        <v>2.32</v>
+        <v>0.8</v>
       </c>
       <c r="G6" t="n">
-        <v>2938</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>14.55</v>
+        <v>0.55</v>
       </c>
       <c r="I6" t="n">
-        <v>14.85</v>
+        <v>17651</v>
       </c>
       <c r="J6" t="n">
-        <v>15.44</v>
-      </c>
-      <c r="K6" t="n">
-        <v>84.19</v>
-      </c>
-      <c r="L6" t="n">
-        <v>185.43</v>
-      </c>
+        <v>16.09</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>1677775.19</v>
+        <v>32.2</v>
       </c>
       <c r="N6" t="n">
-        <v>54.96</v>
+        <v>1372183.55</v>
       </c>
       <c r="O6" t="n">
-        <v>14.34</v>
+        <v>44.57</v>
       </c>
       <c r="P6" t="n">
-        <v>3.85</v>
+        <v>9.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>24394</v>
+        <v>1.65</v>
       </c>
       <c r="R6" t="n">
-        <v>3933</v>
+        <v>50351</v>
       </c>
       <c r="S6" t="n">
-        <v>24</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>79</v>
+        <v>20829</v>
+      </c>
+      <c r="T6" t="n">
+        <v>36</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
       </c>
       <c r="V6" t="n">
-        <v>18.28200866249903</v>
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>65.88004576104804</v>
+      </c>
+      <c r="X6" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>24.29479715622616</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -906,72 +966,81 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29.79</v>
+        <v>1349</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09</v>
+        <v>11.94</v>
       </c>
       <c r="E7" t="n">
-        <v>87.52</v>
+        <v>36.31</v>
       </c>
       <c r="F7" t="n">
-        <v>1.13</v>
+        <v>0.43</v>
       </c>
       <c r="G7" t="n">
-        <v>20117</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>13.2</v>
+        <v>1.73</v>
       </c>
       <c r="I7" t="n">
-        <v>11.24</v>
+        <v>841</v>
       </c>
       <c r="J7" t="n">
-        <v>12.47</v>
+        <v>36.31</v>
       </c>
       <c r="K7" t="n">
-        <v>83.59</v>
+        <v>73.11</v>
       </c>
       <c r="L7" t="n">
-        <v>40</v>
+        <v>69.52</v>
       </c>
       <c r="M7" t="n">
-        <v>1112279.92</v>
+        <v>23.8</v>
       </c>
       <c r="N7" t="n">
-        <v>35.99</v>
+        <v>571322.04</v>
       </c>
       <c r="O7" t="n">
-        <v>8.970000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="P7" t="n">
-        <v>4.1</v>
+        <v>11.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>153670</v>
+        <v>3.46</v>
       </c>
       <c r="R7" t="n">
-        <v>26248</v>
+        <v>12375</v>
       </c>
       <c r="S7" t="n">
-        <v>24</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
+        <v>1477</v>
+      </c>
+      <c r="T7" t="n">
+        <v>16</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="V7" t="n">
-        <v>15.21650079880636</v>
+        <v>8</v>
+      </c>
+      <c r="W7" t="n">
+        <v>65.57351320201516</v>
+      </c>
+      <c r="X7" t="n">
+        <v>78.61076524612234</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>68.36335197744833</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -980,72 +1049,81 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>34.4</v>
+        <v>5670</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02</v>
+        <v>12.91</v>
       </c>
       <c r="E8" t="n">
-        <v>82.73999999999999</v>
+        <v>22.9</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="G8" t="n">
-        <v>667</v>
+        <v>31.93</v>
       </c>
       <c r="H8" t="n">
-        <v>17.96</v>
+        <v>1.29</v>
       </c>
       <c r="I8" t="n">
-        <v>29.17</v>
+        <v>1752</v>
       </c>
       <c r="J8" t="n">
-        <v>28.47</v>
+        <v>30.33</v>
       </c>
       <c r="K8" t="n">
-        <v>83.34</v>
+        <v>24.78</v>
       </c>
       <c r="L8" t="n">
-        <v>53.8</v>
+        <v>12.24</v>
       </c>
       <c r="M8" t="n">
-        <v>1258520.29</v>
+        <v>34.1</v>
       </c>
       <c r="N8" t="n">
-        <v>60.44</v>
+        <v>1347046.9</v>
       </c>
       <c r="O8" t="n">
-        <v>5.74</v>
+        <v>64.52</v>
       </c>
       <c r="P8" t="n">
-        <v>1.08</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>4270</v>
+        <v>4.43</v>
       </c>
       <c r="R8" t="n">
-        <v>1111</v>
+        <v>35517</v>
       </c>
       <c r="S8" t="n">
-        <v>34</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U8" t="n">
-        <v>47</v>
+        <v>4585</v>
+      </c>
+      <c r="T8" t="n">
+        <v>18</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
       </c>
       <c r="V8" t="n">
-        <v>76.46921430165466</v>
+        <v>42</v>
+      </c>
+      <c r="W8" t="n">
+        <v>61.96385759189477</v>
+      </c>
+      <c r="X8" t="n">
+        <v>88.62519542917676</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>42.13101535214459</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1054,72 +1132,81 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>36.31</v>
+        <v>6104</v>
       </c>
       <c r="D9" t="n">
-        <v>0.43</v>
+        <v>15.66</v>
       </c>
       <c r="E9" t="n">
-        <v>8.039999999999999</v>
+        <v>29.68</v>
       </c>
       <c r="F9" t="n">
-        <v>1.73</v>
+        <v>0.13</v>
       </c>
       <c r="G9" t="n">
-        <v>841</v>
+        <v>41</v>
       </c>
       <c r="H9" t="n">
-        <v>36.31</v>
+        <v>1.19</v>
       </c>
       <c r="I9" t="n">
-        <v>73.11</v>
+        <v>3556</v>
       </c>
       <c r="J9" t="n">
-        <v>69.52</v>
+        <v>13.03</v>
       </c>
       <c r="K9" t="n">
-        <v>80.95</v>
+        <v>20.28</v>
       </c>
       <c r="L9" t="n">
-        <v>23.8</v>
+        <v>20.97</v>
       </c>
       <c r="M9" t="n">
-        <v>571322.04</v>
+        <v>41.75</v>
       </c>
       <c r="N9" t="n">
-        <v>8.65</v>
+        <v>2126725.18</v>
       </c>
       <c r="O9" t="n">
-        <v>11.82</v>
+        <v>73.37</v>
       </c>
       <c r="P9" t="n">
-        <v>3.46</v>
+        <v>3.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>12375</v>
+        <v>2.42</v>
       </c>
       <c r="R9" t="n">
-        <v>1477</v>
+        <v>35495</v>
       </c>
       <c r="S9" t="n">
-        <v>16</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U9" t="n">
-        <v>8</v>
+        <v>5558</v>
+      </c>
+      <c r="T9" t="n">
+        <v>21</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
       </c>
       <c r="V9" t="n">
-        <v>68.36335197744833</v>
+        <v>58</v>
+      </c>
+      <c r="W9" t="n">
+        <v>61.26515014988838</v>
+      </c>
+      <c r="X9" t="n">
+        <v>87.69272017291998</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>17.80103767695105</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1128,72 +1215,81 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.01</v>
+        <v>25210</v>
       </c>
       <c r="D10" t="n">
-        <v>0.08</v>
+        <v>17.08</v>
       </c>
       <c r="E10" t="n">
-        <v>46.46</v>
+        <v>29.79</v>
       </c>
       <c r="F10" t="n">
-        <v>1.11</v>
+        <v>0.09</v>
       </c>
       <c r="G10" t="n">
-        <v>15840</v>
+        <v>87.52</v>
       </c>
       <c r="H10" t="n">
-        <v>12.71</v>
+        <v>1.13</v>
       </c>
       <c r="I10" t="n">
-        <v>9.19</v>
+        <v>20117</v>
       </c>
       <c r="J10" t="n">
-        <v>9.41</v>
+        <v>13.2</v>
       </c>
       <c r="K10" t="n">
-        <v>80.11</v>
+        <v>11.24</v>
       </c>
       <c r="L10" t="n">
-        <v>29.6</v>
+        <v>12.47</v>
       </c>
       <c r="M10" t="n">
-        <v>412593.29</v>
+        <v>40</v>
       </c>
       <c r="N10" t="n">
-        <v>63.63</v>
+        <v>1112279.92</v>
       </c>
       <c r="O10" t="n">
-        <v>5.44</v>
+        <v>35.99</v>
       </c>
       <c r="P10" t="n">
-        <v>1.99</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>109913</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>15710</v>
+        <v>153670</v>
       </c>
       <c r="S10" t="n">
-        <v>22</v>
-      </c>
-      <c r="T10" t="inlineStr">
+        <v>26248</v>
+      </c>
+      <c r="T10" t="n">
+        <v>24</v>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="U10" t="n">
-        <v>90</v>
-      </c>
       <c r="V10" t="n">
-        <v>13.39647732977698</v>
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>60.72864355840955</v>
+      </c>
+      <c r="X10" t="n">
+        <v>85.04353517246395</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>15.21650079880636</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1202,66 +1298,75 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29.68</v>
+        <v>3724</v>
       </c>
       <c r="D11" t="n">
-        <v>0.13</v>
+        <v>24.2</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>22.17</v>
       </c>
       <c r="F11" t="n">
-        <v>1.19</v>
+        <v>0.02</v>
       </c>
       <c r="G11" t="n">
-        <v>3556</v>
+        <v>114.71</v>
       </c>
       <c r="H11" t="n">
-        <v>13.03</v>
+        <v>0.72</v>
       </c>
       <c r="I11" t="n">
-        <v>20.28</v>
+        <v>890</v>
       </c>
       <c r="J11" t="n">
-        <v>20.97</v>
+        <v>11.04</v>
       </c>
       <c r="K11" t="n">
-        <v>78.11</v>
+        <v>12.68</v>
       </c>
       <c r="L11" t="n">
-        <v>41.75</v>
+        <v>12.51</v>
       </c>
       <c r="M11" t="n">
-        <v>2126725.18</v>
+        <v>31.1</v>
       </c>
       <c r="N11" t="n">
-        <v>73.37</v>
+        <v>222391.83</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>15.62</v>
       </c>
       <c r="P11" t="n">
-        <v>2.42</v>
+        <v>13.61</v>
       </c>
       <c r="Q11" t="n">
-        <v>35495</v>
+        <v>4.41</v>
       </c>
       <c r="R11" t="n">
-        <v>5558</v>
+        <v>16536</v>
       </c>
       <c r="S11" t="n">
-        <v>21</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="U11" t="n">
-        <v>58</v>
+        <v>4001</v>
+      </c>
+      <c r="T11" t="n">
+        <v>26</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="V11" t="n">
-        <v>17.80103767695105</v>
+        <v>35</v>
+      </c>
+      <c r="W11" t="n">
+        <v>57.92745860618593</v>
+      </c>
+      <c r="X11" t="n">
+        <v>59.42536569985521</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>23.776441520116</v>
       </c>
     </row>
     <row r="12">
@@ -1276,65 +1381,74 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>4543</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="E12" t="n">
         <v>19.74</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>51.71</v>
       </c>
-      <c r="F12" t="n">
+      <c r="H12" t="n">
         <v>0.72</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>509</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>12.64</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>23.39</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>23.84</v>
       </c>
-      <c r="K12" t="n">
-        <v>77.73</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>26.5</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2441803.28</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>11.73</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>10.19</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>0.09</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>28011</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>5578</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>28</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>12</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
+        <v>56.16119256518003</v>
+      </c>
+      <c r="X12" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y12" t="n">
         <v>13.71726615103832</v>
       </c>
     </row>
@@ -1350,65 +1464,74 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>15018</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="E13" t="n">
         <v>15.35</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>5.95</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>0.23</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>8250</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>19.58</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>14.91</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>14.87</v>
       </c>
-      <c r="K13" t="n">
-        <v>77.59</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>12.9</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>675598.01</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>48.9</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>2.31</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>1.16</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>26711</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>8104</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>58</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>16</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
+        <v>53.85496094664723</v>
+      </c>
+      <c r="X13" t="n">
+        <v>61.50582955610891</v>
+      </c>
+      <c r="Y13" t="n">
         <v>28.63193631184944</v>
       </c>
     </row>
@@ -1424,72 +1547,81 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>18266</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="E14" t="n">
         <v>77.67</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>0.1</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>3.54</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>20445</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>10.34</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>8.76</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>8.56</v>
       </c>
-      <c r="K14" t="n">
-        <v>77.19</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>17.18</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>1124597.5</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>30.8</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>2.48</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>1.26</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>221113</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>15547</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>14</v>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>36</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
+        <v>52.10305469635843</v>
+      </c>
+      <c r="X14" t="n">
+        <v>58.12786601201406</v>
+      </c>
+      <c r="Y14" t="n">
         <v>17.59282162428875</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1498,72 +1630,81 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20.78</v>
+        <v>22448</v>
       </c>
       <c r="D15" t="n">
-        <v>0.05</v>
+        <v>14.29</v>
       </c>
       <c r="E15" t="n">
-        <v>54.33</v>
+        <v>23.01</v>
       </c>
       <c r="F15" t="n">
-        <v>1.03</v>
+        <v>0.08</v>
       </c>
       <c r="G15" t="n">
-        <v>955</v>
+        <v>46.46</v>
       </c>
       <c r="H15" t="n">
-        <v>11.84</v>
+        <v>1.11</v>
       </c>
       <c r="I15" t="n">
-        <v>13.49</v>
+        <v>15840</v>
       </c>
       <c r="J15" t="n">
-        <v>13.56</v>
+        <v>12.71</v>
       </c>
       <c r="K15" t="n">
-        <v>76.73999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="L15" t="n">
-        <v>29.7</v>
+        <v>9.41</v>
       </c>
       <c r="M15" t="n">
-        <v>162274.18</v>
+        <v>29.6</v>
       </c>
       <c r="N15" t="n">
-        <v>36.12</v>
+        <v>412593.29</v>
       </c>
       <c r="O15" t="n">
-        <v>12.3</v>
+        <v>63.63</v>
       </c>
       <c r="P15" t="n">
-        <v>1.01</v>
+        <v>5.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>12383</v>
+        <v>1.99</v>
       </c>
       <c r="R15" t="n">
-        <v>1747</v>
+        <v>109913</v>
       </c>
       <c r="S15" t="n">
+        <v>15710</v>
+      </c>
+      <c r="T15" t="n">
         <v>22</v>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="U15" t="n">
-        <v>47</v>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
       </c>
       <c r="V15" t="n">
-        <v>19.2998469335665</v>
+        <v>90</v>
+      </c>
+      <c r="W15" t="n">
+        <v>52.02365587809376</v>
+      </c>
+      <c r="X15" t="n">
+        <v>59.80231578492935</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.39647732977698</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1572,74 +1713,81 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15.72</v>
+        <v>2724</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>14.11</v>
+      </c>
+      <c r="E16" t="n">
+        <v>20.78</v>
       </c>
       <c r="F16" t="n">
-        <v>0.32</v>
+        <v>0.05</v>
       </c>
       <c r="G16" t="n">
-        <v>486</v>
+        <v>54.33</v>
       </c>
       <c r="H16" t="n">
-        <v>12.91</v>
+        <v>1.03</v>
       </c>
       <c r="I16" t="n">
-        <v>12.84</v>
+        <v>955</v>
       </c>
       <c r="J16" t="n">
-        <v>11.14</v>
+        <v>11.84</v>
       </c>
       <c r="K16" t="n">
-        <v>72.98</v>
+        <v>13.49</v>
       </c>
       <c r="L16" t="n">
-        <v>22.5</v>
+        <v>13.56</v>
       </c>
       <c r="M16" t="n">
-        <v>1271789.21</v>
+        <v>29.7</v>
       </c>
       <c r="N16" t="n">
-        <v>49</v>
+        <v>162274.18</v>
       </c>
       <c r="O16" t="n">
-        <v>7.86</v>
+        <v>36.12</v>
       </c>
       <c r="P16" t="n">
-        <v>3.46</v>
+        <v>12.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>20487</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
-        <v>1919</v>
+        <v>12383</v>
       </c>
       <c r="S16" t="n">
-        <v>2577</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U16" t="n">
-        <v>28</v>
+        <v>1747</v>
+      </c>
+      <c r="T16" t="n">
+        <v>22</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
       </c>
       <c r="V16" t="n">
-        <v>18.98796206427069</v>
+        <v>47</v>
+      </c>
+      <c r="W16" t="n">
+        <v>52.0211285404193</v>
+      </c>
+      <c r="X16" t="n">
+        <v>63.55664439952042</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>19.2998469335665</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1648,146 +1796,164 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.9</v>
+        <v>12135</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1</v>
+        <v>19.82</v>
       </c>
       <c r="E17" t="n">
-        <v>31.93</v>
+        <v>15.09</v>
       </c>
       <c r="F17" t="n">
-        <v>1.29</v>
+        <v>0.05</v>
       </c>
       <c r="G17" t="n">
-        <v>1752</v>
+        <v>58.33</v>
       </c>
       <c r="H17" t="n">
-        <v>30.33</v>
+        <v>0.57</v>
       </c>
       <c r="I17" t="n">
-        <v>24.78</v>
+        <v>11372</v>
       </c>
       <c r="J17" t="n">
-        <v>12.24</v>
+        <v>10.78</v>
       </c>
       <c r="K17" t="n">
-        <v>72.55</v>
+        <v>24.54</v>
       </c>
       <c r="L17" t="n">
-        <v>34.1</v>
+        <v>29.46</v>
       </c>
       <c r="M17" t="n">
-        <v>1347046.9</v>
+        <v>17.3</v>
       </c>
       <c r="N17" t="n">
-        <v>64.52</v>
+        <v>1339586.09</v>
       </c>
       <c r="O17" t="n">
-        <v>2.38</v>
+        <v>37.9</v>
       </c>
       <c r="P17" t="n">
-        <v>4.43</v>
+        <v>6.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>35517</v>
+        <v>3.88</v>
       </c>
       <c r="R17" t="n">
-        <v>4585</v>
+        <v>48497</v>
       </c>
       <c r="S17" t="n">
-        <v>18</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="U17" t="n">
-        <v>42</v>
+        <v>9610</v>
+      </c>
+      <c r="T17" t="n">
+        <v>28</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
       </c>
       <c r="V17" t="n">
-        <v>42.13101535214459</v>
+        <v>34</v>
+      </c>
+      <c r="W17" t="n">
+        <v>50.96536737685161</v>
+      </c>
+      <c r="X17" t="n">
+        <v>44.6485862749794</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13.12675558948349</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mar 2024</t>
+          <t>Sep 2024</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.17</v>
+        <v>1670</v>
       </c>
       <c r="D18" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.02</v>
       </c>
-      <c r="E18" t="n">
-        <v>114.71</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.72</v>
-      </c>
       <c r="G18" t="n">
-        <v>890</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>11.04</v>
+        <v>0.88</v>
       </c>
       <c r="I18" t="n">
-        <v>12.68</v>
+        <v>1168</v>
       </c>
       <c r="J18" t="n">
-        <v>12.51</v>
+        <v>11.19</v>
       </c>
       <c r="K18" t="n">
-        <v>72.52</v>
+        <v>19.85</v>
       </c>
       <c r="L18" t="n">
-        <v>31.1</v>
+        <v>19.64</v>
       </c>
       <c r="M18" t="n">
-        <v>222391.83</v>
+        <v>25.6</v>
       </c>
       <c r="N18" t="n">
-        <v>15.62</v>
+        <v>1191331.95</v>
       </c>
       <c r="O18" t="n">
-        <v>13.61</v>
+        <v>33.32</v>
       </c>
       <c r="P18" t="n">
-        <v>4.41</v>
+        <v>9.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>16536</v>
+        <v>3.69</v>
       </c>
       <c r="R18" t="n">
-        <v>4001</v>
+        <v>22240</v>
       </c>
       <c r="S18" t="n">
-        <v>26</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U18" t="n">
-        <v>35</v>
+        <v>2718</v>
+      </c>
+      <c r="T18" t="n">
+        <v>14</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
       </c>
       <c r="V18" t="n">
-        <v>23.776441520116</v>
+        <v>16</v>
+      </c>
+      <c r="W18" t="n">
+        <v>50.59396623685769</v>
+      </c>
+      <c r="X18" t="n">
+        <v>55.2180951266328</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>18.99870072744285</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1796,148 +1962,166 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15.75</v>
+        <v>2407</v>
       </c>
       <c r="D19" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="E19" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="F19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4936</v>
-      </c>
       <c r="H19" t="n">
-        <v>10.51</v>
+        <v>0.32</v>
       </c>
       <c r="I19" t="n">
-        <v>12.01</v>
+        <v>486</v>
       </c>
       <c r="J19" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="K19" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="L19" t="n">
         <v>11.14</v>
       </c>
-      <c r="K19" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L19" t="n">
-        <v>23.67</v>
-      </c>
       <c r="M19" t="n">
-        <v>1503863.63</v>
+        <v>22.5</v>
       </c>
       <c r="N19" t="n">
-        <v>20.78</v>
+        <v>1271789.21</v>
       </c>
       <c r="O19" t="n">
-        <v>8.26</v>
+        <v>49</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>7.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>141858</v>
+        <v>3.46</v>
       </c>
       <c r="R19" t="n">
-        <v>13488</v>
+        <v>20487</v>
       </c>
       <c r="S19" t="n">
-        <v>13</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U19" t="n">
-        <v>29</v>
+        <v>1919</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2577</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
       </c>
       <c r="V19" t="n">
-        <v>26.32364432616601</v>
+        <v>28</v>
+      </c>
+      <c r="W19" t="n">
+        <v>49.39652873350715</v>
+      </c>
+      <c r="X19" t="n">
+        <v>44.03206779015759</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>18.98796206427069</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sep 2024</t>
+          <t>Mar 2024</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.7</v>
+        <v>157284</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02</v>
+        <v>28.89</v>
       </c>
       <c r="E20" t="n">
-        <v>67.15000000000001</v>
+        <v>17.99</v>
       </c>
       <c r="F20" t="n">
-        <v>0.88</v>
+        <v>6.45</v>
       </c>
       <c r="G20" t="n">
-        <v>1168</v>
+        <v>1.3</v>
       </c>
       <c r="H20" t="n">
-        <v>11.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>19.85</v>
+        <v>12547</v>
       </c>
       <c r="J20" t="n">
-        <v>19.64</v>
+        <v>17.25</v>
       </c>
       <c r="K20" t="n">
-        <v>66.98</v>
+        <v>51.95</v>
       </c>
       <c r="L20" t="n">
-        <v>25.6</v>
+        <v>55.18</v>
       </c>
       <c r="M20" t="n">
-        <v>1191331.95</v>
+        <v>7.6</v>
       </c>
       <c r="N20" t="n">
-        <v>33.32</v>
+        <v>1319221.86</v>
       </c>
       <c r="O20" t="n">
-        <v>9.25</v>
+        <v>25.76</v>
       </c>
       <c r="P20" t="n">
-        <v>3.69</v>
+        <v>6.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>22240</v>
+        <v>3.43</v>
       </c>
       <c r="R20" t="n">
-        <v>2718</v>
+        <v>159516</v>
       </c>
       <c r="S20" t="n">
-        <v>14</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="U20" t="n">
+        <v>46081</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-14152</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
         <v>16</v>
       </c>
-      <c r="V20" t="n">
-        <v>18.99870072744285</v>
+      <c r="W20" t="n">
+        <v>48.83992353907501</v>
+      </c>
+      <c r="X20" t="n">
+        <v>42.47098526296872</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>21.39660074377121</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1946,72 +2130,83 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17.07</v>
+        <v>16801</v>
       </c>
       <c r="D21" t="n">
-        <v>0.04</v>
+        <v>9.51</v>
       </c>
       <c r="E21" t="n">
-        <v>25.36</v>
+        <v>15.75</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>335</v>
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="H21" t="n">
-        <v>13.04</v>
+        <v>1.23</v>
       </c>
       <c r="I21" t="n">
-        <v>10.03</v>
+        <v>4936</v>
       </c>
       <c r="J21" t="n">
-        <v>9</v>
+        <v>10.51</v>
       </c>
       <c r="K21" t="n">
-        <v>64.59999999999999</v>
+        <v>12.01</v>
       </c>
       <c r="L21" t="n">
-        <v>24.4</v>
+        <v>11.14</v>
       </c>
       <c r="M21" t="n">
-        <v>2521508.87</v>
+        <v>23.67</v>
       </c>
       <c r="N21" t="n">
-        <v>45.41</v>
+        <v>1503863.63</v>
       </c>
       <c r="O21" t="n">
-        <v>14.08</v>
+        <v>20.78</v>
       </c>
       <c r="P21" t="n">
-        <v>2.6</v>
+        <v>8.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>18590</v>
+        <v>1.78</v>
       </c>
       <c r="R21" t="n">
-        <v>1271</v>
+        <v>141858</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="U21" t="n">
-        <v>44</v>
+        <v>13488</v>
+      </c>
+      <c r="T21" t="n">
+        <v>13</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="V21" t="n">
-        <v>21.14089015706202</v>
+        <v>29</v>
+      </c>
+      <c r="W21" t="n">
+        <v>46.94201315314325</v>
+      </c>
+      <c r="X21" t="n">
+        <v>31.86080183638076</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>26.32364432616601</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2020,66 +2215,75 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17.99</v>
+        <v>1953</v>
       </c>
       <c r="D22" t="n">
-        <v>6.45</v>
+        <v>6.84</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3</v>
+        <v>17.07</v>
       </c>
       <c r="F22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G22" t="n">
-        <v>12547</v>
+        <v>25.36</v>
       </c>
       <c r="H22" t="n">
-        <v>17.25</v>
+        <v>1.5</v>
       </c>
       <c r="I22" t="n">
-        <v>51.95</v>
+        <v>335</v>
       </c>
       <c r="J22" t="n">
-        <v>55.18</v>
+        <v>13.04</v>
       </c>
       <c r="K22" t="n">
-        <v>63.6</v>
+        <v>10.03</v>
       </c>
       <c r="L22" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>1319221.86</v>
+        <v>24.4</v>
       </c>
       <c r="N22" t="n">
-        <v>25.76</v>
+        <v>2521508.87</v>
       </c>
       <c r="O22" t="n">
-        <v>6.2</v>
+        <v>45.41</v>
       </c>
       <c r="P22" t="n">
-        <v>3.43</v>
+        <v>14.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>159516</v>
+        <v>2.6</v>
       </c>
       <c r="R22" t="n">
-        <v>46081</v>
+        <v>18590</v>
       </c>
       <c r="S22" t="n">
-        <v>-14152</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U22" t="n">
-        <v>16</v>
+        <v>1271</v>
+      </c>
+      <c r="T22" t="n">
+        <v>10</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
       </c>
       <c r="V22" t="n">
-        <v>21.39660074377121</v>
+        <v>44</v>
+      </c>
+      <c r="W22" t="n">
+        <v>45.18874127254222</v>
+      </c>
+      <c r="X22" t="n">
+        <v>44.79593191208912</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>21.14089015706202</v>
       </c>
     </row>
     <row r="23">
@@ -2094,65 +2298,74 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>15046</v>
+      </c>
+      <c r="D23" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="E23" t="n">
         <v>16.72</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>14.87</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>1.61</v>
       </c>
-      <c r="F23" t="n">
+      <c r="H23" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G23" t="n">
+      <c r="I23" t="n">
         <v>13296</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>18.18</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>85.78</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>53.42</v>
       </c>
-      <c r="K23" t="n">
-        <v>59.34</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>6.63</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>496415.88</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>36.74</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>12.61</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>3.81</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>110519</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>15401</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>-7745</v>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>19</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
+        <v>42.60305121511472</v>
+      </c>
+      <c r="X23" t="n">
+        <v>24.97874389217935</v>
+      </c>
+      <c r="Y23" t="n">
         <v>16.30293930023252</v>
       </c>
     </row>
